--- a/harmonogram.xlsx
+++ b/harmonogram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kubak\Desktop\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D72E1EA9-5F74-4917-822F-ED3909A8454D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D4B624-F670-4039-A0BB-C9CC1790833F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5541C825-59C0-4E5F-ACA2-E98AA58ECD95}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
   <si>
     <t>Dawid</t>
   </si>
@@ -63,6 +63,18 @@
   </si>
   <si>
     <t>Znalezienie algorytmu do najkrótszej drogi w cyklu i znalezienia strzelca</t>
+  </si>
+  <si>
+    <t>Wyjazd służbowy</t>
+  </si>
+  <si>
+    <t>Szukanie algortymu sensu życia</t>
+  </si>
+  <si>
+    <t>Implementacja algorytmu najkrótszej drogi</t>
+  </si>
+  <si>
+    <t>Wczytywanie danych do JS</t>
   </si>
 </sst>
 </file>
@@ -527,18 +539,28 @@
         <v>46120</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+    <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="E4" s="5">
         <v>46127</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="5">

--- a/harmonogram.xlsx
+++ b/harmonogram.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kubak\Desktop\temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kubak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D4B624-F670-4039-A0BB-C9CC1790833F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D9F593D-D3B1-46FC-A540-41BD1A9A352F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5541C825-59C0-4E5F-ACA2-E98AA58ECD95}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="18">
   <si>
     <t>Dawid</t>
   </si>
@@ -75,6 +75,21 @@
   </si>
   <si>
     <t>Wczytywanie danych do JS</t>
+  </si>
+  <si>
+    <t>Prace organizacyjne</t>
+  </si>
+  <si>
+    <t>Modyfikacje generatora: liczba kopalni &lt;= liczba domków; każdy domek ma być połączony z każdą kopalnią; generowane dane mają zapisywać się do pliku; naprawić błąd kopalni bez ścieżek;</t>
+  </si>
+  <si>
+    <t>Modyfikacja wyświetlania: kopalnia po najechaniu na nią myszką ma pokazywać pojemność; naprawić błąd, przez który domki i kopalnie wyświetlają się na sobie; czym są przerywane kreski na mapie xd</t>
+  </si>
+  <si>
+    <t>Napisanie algorytmu strzelców na odcinkach otoczki wypukłej</t>
+  </si>
+  <si>
+    <t>Napisać i zaimplementować algorytm Boyera i Moora do kopmresji pliku z danymi jsona</t>
   </si>
 </sst>
 </file>
@@ -479,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D9BB1C2-395D-48E4-9475-9BC7BBE93EDA}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.21875" customWidth="1"/>
@@ -557,41 +572,124 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E5" s="5">
         <v>46134</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E6" s="5">
         <v>46141</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E7" s="5">
         <v>46148</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E8" s="5">
         <v>46155</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="5">
+        <v>46162</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="5">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="5">
+        <v>46176</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="5">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="5">
+        <v>46190</v>
       </c>
     </row>
   </sheetData>

--- a/harmonogram.xlsx
+++ b/harmonogram.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="27">
   <si>
     <t>Dawid</t>
   </si>
@@ -96,13 +96,28 @@
   </si>
   <si>
     <t>Sprawdzenie programu pod kątem błędów, naprawić odpalanie index.html (blokuje CORS)</t>
+  </si>
+  <si>
+    <t>Przygotowanie testów i poprawa bledów</t>
+  </si>
+  <si>
+    <t>Utworzenie nowego algorytmu najkrotszej drogi, implementacja wyszukiwarki</t>
+  </si>
+  <si>
+    <t>Dokumentacja</t>
+  </si>
+  <si>
+    <t>Przygtoowanie komentarzy do dokumentacji</t>
+  </si>
+  <si>
+    <t>PREZENTACJA :D</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -111,8 +126,16 @@
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -125,8 +148,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -149,11 +178,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -168,6 +234,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -495,7 +573,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -503,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="29.25" customWidth="1"/>
@@ -699,25 +777,56 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+    <row r="12" spans="1:5" ht="42.75">
+      <c r="A12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>22</v>
+      </c>
       <c r="E12" s="5">
         <v>46183</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+    <row r="13" spans="1:5" ht="28.5">
+      <c r="A13" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>24</v>
+      </c>
       <c r="E13" s="5">
-        <v>46190</v>
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="5">
+        <v>46192</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A14:D14"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>